--- a/data/trans_dic/P57_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57_R-Provincia-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,54; 35,81</t>
+          <t>24,81; 36,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,11</t>
+          <t>3,62; 8,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,44; 36,67</t>
+          <t>25,51; 36,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,58</t>
+          <t>4,36; 8,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,53; 34,38</t>
+          <t>26,37; 34,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,94</t>
+          <t>4,59; 8,08</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,45; 17,84</t>
+          <t>11,5; 18,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,83</t>
+          <t>3,37; 8,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 18,21</t>
+          <t>11,83; 18,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 8,1</t>
+          <t>4,56; 8,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 16,85</t>
+          <t>12,42; 17,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 7,71</t>
+          <t>4,34; 7,52</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 11,98</t>
+          <t>5,75; 11,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,73; 24,15</t>
+          <t>15,76; 23,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,66; 20,02</t>
+          <t>11,61; 19,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,37; 24,79</t>
+          <t>17,38; 24,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 15,11</t>
+          <t>9,76; 14,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 23,1</t>
+          <t>17,72; 22,89</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,65; 20,6</t>
+          <t>12,08; 19,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,92; 17,37</t>
+          <t>9,07; 17,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,74; 32,9</t>
+          <t>23,51; 33,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 13,72</t>
+          <t>6,21; 13,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,05; 25,6</t>
+          <t>18,91; 25,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 13,97</t>
+          <t>8,0; 14,0</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,5; 41,1</t>
+          <t>28,25; 40,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,56</t>
+          <t>4,65; 10,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,99; 48,21</t>
+          <t>35,45; 48,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 11,88</t>
+          <t>6,75; 11,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,5; 42,8</t>
+          <t>33,42; 42,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,16</t>
+          <t>6,42; 10,08</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,32; 23,71</t>
+          <t>14,51; 24,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,31; 25,65</t>
+          <t>17,19; 25,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,76; 27,14</t>
+          <t>16,95; 26,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,94; 26,48</t>
+          <t>19,49; 26,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,87; 24,22</t>
+          <t>16,99; 23,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,98; 24,65</t>
+          <t>19,12; 24,76</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,46; 19,67</t>
+          <t>13,6; 19,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,03; 11,87</t>
+          <t>7,11; 11,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,33; 23,95</t>
+          <t>17,7; 24,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,72</t>
+          <t>4,76; 13,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,58; 20,9</t>
+          <t>16,58; 21,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,75; 11,67</t>
+          <t>6,08; 11,73</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,02; 22,83</t>
+          <t>17,0; 22,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,28; 23,74</t>
+          <t>7,58; 23,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,21; 28,75</t>
+          <t>22,33; 29,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31,42; 37,32</t>
+          <t>31,36; 37,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,65; 24,79</t>
+          <t>20,61; 24,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,96; 29,13</t>
+          <t>14,94; 29,37</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,16; 19,78</t>
+          <t>17,26; 19,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,88</t>
+          <t>9,62; 13,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,11; 25,03</t>
+          <t>21,94; 24,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,85; 17,37</t>
+          <t>12,66; 17,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,07; 22,14</t>
+          <t>20,09; 22,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,3; 15,33</t>
+          <t>12,52; 15,33</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>71866; 104876</t>
+          <t>72663; 105827</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11471; 28359</t>
+          <t>11270; 27223</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73436; 105875</t>
+          <t>73653; 106202</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13063; 24842</t>
+          <t>12634; 24994</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>154308; 199944</t>
+          <t>153352; 199546</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27401; 47722</t>
+          <t>27599; 48579</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57198; 89096</t>
+          <t>57408; 90062</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18075; 45758</t>
+          <t>17474; 44520</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60077; 94905</t>
+          <t>61653; 96285</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23205; 41405</t>
+          <t>23331; 41302</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>127816; 171978</t>
+          <t>126760; 174865</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45010; 79404</t>
+          <t>44662; 77381</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19289; 38072</t>
+          <t>18263; 37724</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49425; 75900</t>
+          <t>49541; 75020</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39223; 67333</t>
+          <t>39040; 66384</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60362; 86145</t>
+          <t>60395; 84362</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63519; 98829</t>
+          <t>63825; 96953</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>115312; 152863</t>
+          <t>117254; 151473</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46423; 75573</t>
+          <t>44329; 72846</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27240; 53064</t>
+          <t>27707; 54129</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91359; 126612</t>
+          <t>90468; 127110</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25611; 63810</t>
+          <t>28889; 64938</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>143237; 192487</t>
+          <t>142147; 191943</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>62725; 107661</t>
+          <t>61605; 107891</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>60203; 86817</t>
+          <t>59663; 86497</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8377; 18867</t>
+          <t>8310; 19040</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76491; 105371</t>
+          <t>77492; 106063</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14011; 24550</t>
+          <t>13946; 24234</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>144007; 183943</t>
+          <t>143648; 184662</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24414; 39175</t>
+          <t>24728; 38851</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37671; 62398</t>
+          <t>38182; 63793</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>46666; 69152</t>
+          <t>46360; 68852</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45609; 73855</t>
+          <t>46114; 72643</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48614; 67983</t>
+          <t>50029; 68867</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>90312; 129635</t>
+          <t>90957; 126829</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>99911; 129737</t>
+          <t>100623; 130316</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>87649; 128013</t>
+          <t>88507; 125965</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43842; 73992</t>
+          <t>44329; 73477</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118241; 163407</t>
+          <t>120780; 166404</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36260; 116255</t>
+          <t>40308; 116037</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>221069; 278673</t>
+          <t>221097; 280761</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>84625; 171603</t>
+          <t>89399; 172572</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>132486; 177734</t>
+          <t>132362; 176891</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67530; 220371</t>
+          <t>70327; 222160</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>183068; 236974</t>
+          <t>184038; 239819</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>225023; 267275</t>
+          <t>224558; 266631</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>331008; 397328</t>
+          <t>330277; 399265</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>246023; 478984</t>
+          <t>245709; 482950</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>580009; 668542</t>
+          <t>583378; 673888</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>337766; 478937</t>
+          <t>331725; 479683</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>780032; 882980</t>
+          <t>774090; 877276</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>467756; 632423</t>
+          <t>460815; 630378</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1386274; 1529294</t>
+          <t>1388120; 1525323</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>872095; 1086800</t>
+          <t>887320; 1086718</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57_R-Provincia-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,81; 36,14</t>
+          <t>24,69; 35,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 8,74</t>
+          <t>3,45; 8,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,51; 36,79</t>
+          <t>25,81; 37,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,63</t>
+          <t>4,7; 8,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,37; 34,31</t>
+          <t>26,88; 34,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,08</t>
+          <t>4,62; 7,74</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 18,04</t>
+          <t>11,57; 17,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,59</t>
+          <t>3,5; 8,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,83; 18,47</t>
+          <t>12,08; 18,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,08</t>
+          <t>4,7; 8,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,42; 17,13</t>
+          <t>12,23; 17,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,52</t>
+          <t>4,47; 7,62</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 11,87</t>
+          <t>5,92; 11,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,76; 23,87</t>
+          <t>16,32; 24,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,61; 19,74</t>
+          <t>11,66; 19,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,38; 24,27</t>
+          <t>17,35; 23,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 14,82</t>
+          <t>9,54; 14,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,72; 22,89</t>
+          <t>17,72; 23,07</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,08; 19,85</t>
+          <t>12,33; 19,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,07; 17,72</t>
+          <t>8,34; 16,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,51; 33,03</t>
+          <t>23,1; 32,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 13,97</t>
+          <t>9,66; 15,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 25,53</t>
+          <t>19,09; 25,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,0; 14,0</t>
+          <t>10,21; 14,91</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,25; 40,95</t>
+          <t>27,81; 40,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 10,65</t>
+          <t>4,56; 10,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,45; 48,52</t>
+          <t>35,44; 47,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,72</t>
+          <t>6,59; 11,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,42; 42,96</t>
+          <t>33,46; 42,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,42; 10,08</t>
+          <t>6,23; 9,96</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,51; 24,24</t>
+          <t>14,13; 23,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,19; 25,54</t>
+          <t>18,39; 27,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,95; 26,7</t>
+          <t>17,04; 27,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,49; 26,82</t>
+          <t>19,46; 26,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,99; 23,7</t>
+          <t>16,95; 23,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,12; 24,76</t>
+          <t>20,05; 25,56</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,6; 19,35</t>
+          <t>13,62; 19,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 11,78</t>
+          <t>7,52; 12,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,7; 24,39</t>
+          <t>17,65; 24,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 13,69</t>
+          <t>11,06; 15,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,58; 21,06</t>
+          <t>16,45; 20,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,08; 11,73</t>
+          <t>9,72; 12,95</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,0; 22,72</t>
+          <t>17,17; 22,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,58; 23,94</t>
+          <t>19,39; 25,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,33; 29,1</t>
+          <t>22,54; 28,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31,36; 37,23</t>
+          <t>31,14; 36,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,61; 24,91</t>
+          <t>20,44; 24,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,94; 29,37</t>
+          <t>26,05; 30,31</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -1272,22 +1272,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,26; 19,93</t>
+          <t>17,29; 20,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,62; 13,91</t>
+          <t>12,23; 14,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21,94; 24,87</t>
+          <t>22,03; 24,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,66; 17,32</t>
+          <t>16,15; 18,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,52; 15,33</t>
+          <t>14,67; 16,23</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>38048</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72663; 105827</t>
+          <t>72300; 105101</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11270; 27223</t>
+          <t>11014; 26110</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73653; 106202</t>
+          <t>74501; 107292</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12634; 24994</t>
+          <t>14856; 27581</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>153352; 199546</t>
+          <t>156308; 200834</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27599; 48579</t>
+          <t>29354; 49156</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28414</t>
+          <t>29292</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>32634</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59621</t>
+          <t>61926</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57408; 90062</t>
+          <t>57762; 89591</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17474; 44520</t>
+          <t>18565; 45448</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61653; 96285</t>
+          <t>62959; 97241</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23331; 41302</t>
+          <t>25484; 43905</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>126760; 174865</t>
+          <t>124769; 173980</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44662; 77381</t>
+          <t>47971; 81803</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61468</t>
+          <t>64004</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72370</t>
+          <t>72356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>133839</t>
+          <t>136359</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18263; 37724</t>
+          <t>18805; 37886</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49541; 75020</t>
+          <t>51302; 77554</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39040; 66384</t>
+          <t>39203; 67130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60395; 84362</t>
+          <t>61541; 83842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63825; 96953</t>
+          <t>62409; 96434</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>117254; 151473</t>
+          <t>118563; 154382</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38524</t>
+          <t>43402</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46964</t>
+          <t>51336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85488</t>
+          <t>94739</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44329; 72846</t>
+          <t>45244; 72604</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27707; 54129</t>
+          <t>30473; 59899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90468; 127110</t>
+          <t>88913; 126237</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28889; 64938</t>
+          <t>39591; 64870</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>142147; 191943</t>
+          <t>143546; 189421</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61605; 107891</t>
+          <t>79116; 115555</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>19496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31257</t>
+          <t>34002</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>59663; 86497</t>
+          <t>58739; 86340</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8310; 19040</t>
+          <t>9372; 21161</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77492; 106063</t>
+          <t>77475; 104796</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13946; 24234</t>
+          <t>14927; 25832</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>143648; 184662</t>
+          <t>143826; 183544</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24728; 38851</t>
+          <t>26921; 43041</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>57348</t>
+          <t>60348</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58057</t>
+          <t>60491</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>115405</t>
+          <t>120839</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38182; 63793</t>
+          <t>37167; 62508</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>46360; 68852</t>
+          <t>49775; 73131</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46114; 72643</t>
+          <t>46379; 73726</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50029; 68867</t>
+          <t>51270; 70737</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>90957; 126829</t>
+          <t>90740; 127568</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>100623; 130316</t>
+          <t>107095; 136520</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>57478</t>
+          <t>67989</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82673</t>
+          <t>101669</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>140152</t>
+          <t>169658</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>88507; 125965</t>
+          <t>88684; 126134</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>44329; 73477</t>
+          <t>54042; 86812</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>120780; 166404</t>
+          <t>120411; 164854</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40308; 116037</t>
+          <t>85174; 119676</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>221097; 280761</t>
+          <t>219303; 278887</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89399; 172572</t>
+          <t>144679; 192739</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>155662</t>
+          <t>174462</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>245398</t>
+          <t>283732</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>401060</t>
+          <t>458194</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>132362; 176891</t>
+          <t>133671; 175810</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>70327; 222160</t>
+          <t>154644; 201731</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>184038; 239819</t>
+          <t>185767; 236741</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>224558; 266631</t>
+          <t>258350; 306713</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>330277; 399265</t>
+          <t>327674; 400006</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>245709; 482950</t>
+          <t>423858; 493104</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>429876</t>
+          <t>471807</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>573850</t>
+          <t>641958</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1003726</t>
+          <t>1113764</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>583378; 673888</t>
+          <t>584516; 679576</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>331725; 479683</t>
+          <t>430826; 514378</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>774090; 877276</t>
+          <t>777164; 880662</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>460815; 630378</t>
+          <t>599754; 677803</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1388120; 1525323</t>
+          <t>1388057; 1525720</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>887320; 1086718</t>
+          <t>1061579; 1174508</t>
         </is>
       </c>
     </row>
